--- a/data_extactor/batch_10_fa/batch_0040_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0040_fa.xlsx
@@ -493,7 +493,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Musicians and Singers (نوازندگان و خوانندگان)</t>
+          <t>نوازندگان و خوانندگان (Musicians and Singers)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -508,7 +508,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>صحبت کردن | گوش دادن فعال | نظارت | درک مطلب | تفکر انتقادی</t>
+          <t>سخن گفتن | گوش دادن فعال | نظارت | درک مطلب | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -518,17 +518,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شنیداری | بیان شفاهی | حساسیت شنوایی | حافظه‌سپاری | درک نوشتاری | تشخیص گفتار | توجه شنیداری | وضوح گفتار | دید نزدیک | خلاقیت | سرعت بستن | مهارت انگشتان | مهارت دستی | انعطاف‌پذیری بستن | بیان نوشتاری | ثبات بازو-دست | سرعت ادراکی | نظم‌دهی اطلاعات | روانی ایده‌ها</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت شنوایی | حفظ کردن | درک کتبی | تشخیص گفتار | توجه شنیداری | وضوح گفتار | بینایی نزدیک | اصالت | سرعت بستار | مهارت انگشتان | مهارت دستی | انعطاف‌پذیری بستار | بیان کتبی | ثبات دست و بازو | سرعت ادراکی | ترتیب‌دهی اطلاعات | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>اهمیت دقیق یا صحیح بودن | کار با یا مشارکت در یک گروه یا تیم کاری | مجاورت فیزیکی | تماس با دیگران | صرف زمان برای نشستن | صرف زمان برای استفاده از دست‌ها جهت کنترل، لمس یا کار با اشیاء، ابزارها یا کنترل‌ها | محیط داخلی، دارای کنترل محیطی | فشار زمانی | بحث‌های رودررو با افراد و درون تیم‌ها | سطح رقابت | ایمیل</t>
+          <t>اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | نزدیکی فیزیکی | ارتباط با دیگران | صرف زمان برای نشستن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | محیط داخلی، دارای کنترل شرایط محیطی | فشار زمانی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سطح رقابت | ایمیل</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>بازیگران | معلمان هنر، نمایش و موسیقی، پس از متوسطه | ورزشکاران و رقابت‌کنندگان ورزشی | گویندگان رادیو و تلویزیون و دی‌جی‌های رادیو | طراحان رقص | رقصندگان | دی‌جی‌ها، به جز رادیو | معلمان زبان و ادبیات انگلیسی، پس از متوسطه | هنرمندان تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | مورخان | معلمان دوره متوسطه اول، به جز آموزش ویژه و شغلی/فنی | مدیران موسیقی و آهنگسازان | موسیقی‌درمانگران | تعمیرکاران و کوک‌کنندگان سازهای موسیقی | شاعران، ترانه‌سرایان و نویسندگان خلاق | تهیه‌کنندگان و کارگردانان | معلمان دوره متوسطه دوم، به جز آموزش ویژه و شغلی/فنی | معلمان آموزش‌های تکمیلی | تکنسین‌های مهندسی صدا | مدیران استعداد</t>
+          <t>بازیگران | مدرسان هنر، نمایش و موسیقی، آموزش عالی | ورزشکاران و رقبای ورزشی | گویندگان رادیو و تلویزیون و دی‌جی‌های رادیو | طراحان رقص | رقصندگان | دی‌جی‌ها، به جز رادیو | مدرسان زبان و ادبیات انگلیسی، آموزش عالی | هنرمندان تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | مورخان | معلمان دوره راهنمایی، به استثنای آموزش استثنایی و فنی/حرفه‌ای | مدیران موسیقی و آهنگسازان | موسیقی‌درمانگران | تعمیرکاران و کوک‌کنندگان سازهای موسیقی | شاعران، ترانه‌سرایان و نویسندگان خلاق | تهیه‌کنندگان و کارگردانان | معلمان دبیرستان، به استثنای آموزش ویژه و فنی/حرفه‌ای | معلمان خودسازی | تکنسین‌های مهندسی صدا | مدیران استعداد</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Disc Jockeys, Except Radio (دی‌جی‌ها، به جز رادیو)</t>
+          <t>دی‌جی‌ها، به جز رادیو (Disc Jockeys, Except Radio)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -565,27 +565,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | صحبت کردن | درک مطلب | تفکر انتقادی | نظارت | نوشتن</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>هنرهای زیبا | خدمات مشتری و شخصی | ارتباطات و رسانه | زبان انگلیسی | کامپیوتر و الکترونیک | فروش و بازاریابی | مخابرات</t>
+          <t>هنرهای زیبا | خدمات مشتری و شخصی | ارتباطات و رسانه | زبان انگلیسی | رایانه و الکترونیک | فروش و بازاریابی | مخابرات</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شنیداری | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | نظم‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک نوشتاری | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | اشتراک زمانی | مهارت انگشتان | مهارت دستی | دید دور | حافظه‌سپاری | روانی ایده‌ها | توجه شنیداری | خلاقیت | حساسیت شنوایی | ثبات بازو-دست</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | مهارت انگشتان | مهارت دستی | بینایی دور | حفظ کردن | روانی ایده‌ها | توجه شنیداری | اصالت | حساسیت شنوایی | ثبات دست و بازو</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>تماس با دیگران | تعامل با مشتریان خارجی یا عموم مردم | بحث‌های رودررو با افراد و درون تیم‌ها | مجاورت فیزیکی | صرف زمان برای ایستادن | صرف زمان برای راه رفتن یا دویدن | کار با یا مشارکت در یک گروه یا تیم کاری | مکالمات تلفنی | محیط داخلی، دارای کنترل محیطی | اهمیت تکرار وظایف مشابه | فشار زمانی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | صرف زمان برای استفاده از دست‌ها جهت کنترل، لمس یا کار با اشیاء، ابزارها یا کنترل‌ها | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | قرار گرفتن در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | سطح رقابت | سخنرانی عمومی | ایمیل</t>
+          <t>ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | نزدیکی فیزیکی | صرف زمان برای ایستادن | صرف زمان برای راه رفتن یا دویدن | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت تکرار وظایف یکسان | فشار زمانی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | سطح رقابت | سخنرانی عمومی | ایمیل</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>نمایندگان و مدیران تجاری هنرمندان، مجریان و ورزشکاران | ورزشکاران و رقابت‌کنندگان ورزشی | تکنسین‌های صوتی و تصویری | نصاب‌ها و تعمیرکاران تجهیزات صوتی و تصویری | گویندگان رادیو و تلویزیون و دی‌جی‌های رادیو | تکنسین‌های پخش | طراحان رقص | تظاهرکنندگان و مروجان محصول | تدوینگران فیلم و ویدئو | میزبانان و مهمانداران، رستوران، سالن و کافی‌شاپ | مدیران برنامه‌ریزی رسانه | مدیران فنی رسانه | برنامه‌ریزان جلسات، همایش‌ها و رویدادها | مدیران موسیقی و آهنگسازان | نوازندگان و خوانندگان | تهیه‌کنندگان و کارگردانان | تکنسین‌های مهندسی صدا | هنرمندان و انیماتورهای جلوه‌های ویژه | مدیران استعداد | طراحان بازی‌های ویدئویی</t>
+          <t>نمایندگان و مدیران تجاری هنرمندان، اجراکنندگان و ورزشکاران | ورزشکاران و رقبای ورزشی | تکنسین‌های صوتی و تصویری | نصب‌کنندگان و تعمیرکنندگان تجهیزات صوتی و تصویری | گویندگان رادیو و تلویزیون و دی‌جی‌های رادیو | تکنسین‌های پخش | طراحان رقص | نمایش‌دهندگان و تبلیغ‌کنندگان محصول | تدوینگران فیلم و ویدئو | میزبانان رستوران، سالن و کافی‌شاپ | مدیران برنامه‌ریزی رسانه | مدیران/کارگردانان فنی رسانه | برنامه‌ریزان جلسات، همایش‌ها و رویدادها | مدیران موسیقی و آهنگسازان | نوازندگان و خوانندگان | تهیه‌کنندگان و کارگردانان | تکنسین‌های مهندسی صدا | هنرمندان جلوه‌های ویژه و انیماتورها | مدیران استعداد | طراحان بازی‌های ویدئویی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Entertainers and Performers, Sports and Related Workers, All Other (سرگرم‌کنندگان و مجریان، کارگران ورزشی و مرتبط، سایر)</t>
+          <t>سرگرم‌کنندگان و مجریان، کارگران ورزشی و مرتبط، سایر (Entertainers and Performers, Sports and Related Workers, All Other)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -622,27 +622,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | صحبت کردن | درک مطلب | تفکر انتقادی | نظارت | نوشتن</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>هنرهای زیبا | ارتباطات و رسانه | زبان انگلیسی | خدمات مشتری و شخصی | فروش و بازاریابی | آموزش و پرورش | روانشناسی</t>
+          <t>هنرهای زیبا | ارتباطات و رسانه | زبان انگلیسی | خدمات مشتری و شخصی | فروش و بازاریابی | آموزش و پرورش | روان‌شناسی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شنیداری | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | نظم‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک نوشتاری | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | اشتراک زمانی | مهارت انگشتان | مهارت دستی | دید دور | حافظه‌سپاری | روانی ایده‌ها | خلاقیت | هماهنگی کلی بدن | استقامت | تعادل کلی بدن</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | مهارت انگشتان | مهارت دستی | بینایی دور | حفظ کردن | روانی ایده‌ها | اصالت | هماهنگی کلی بدن | استقامت | تعادل کلی بدن</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>تماس با دیگران | تعامل با مشتریان خارجی یا عموم مردم | بحث‌های رودررو با افراد و درون تیم‌ها | مجاورت فیزیکی | صرف زمان برای ایستادن | صرف زمان برای راه رفتن یا دویدن | کار با یا مشارکت در یک گروه یا تیم کاری | مکالمات تلفنی | محیط داخلی، دارای کنترل محیطی | اهمیت تکرار وظایف مشابه | فشار زمانی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | صرف زمان برای استفاده از دست‌ها جهت کنترل، لمس یا کار با اشیاء، ابزارها یا کنترل‌ها | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | سخنرانی عمومی | سطح رقابت</t>
+          <t>ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | نزدیکی فیزیکی | صرف زمان برای ایستادن | صرف زمان برای راه رفتن یا دویدن | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت تکرار وظایف یکسان | فشار زمانی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | سخنرانی عمومی | سطح رقابت</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>بازیگران | رقصندگان | طراحان رقص | نوازندگان و خوانندگان | مدیران موسیقی و آهنگسازان | دی‌جی‌ها، به جز رادیو | ورزشکاران و رقابت‌کنندگان ورزشی | مربیان و استعدادیاب‌ها | داوران، قضاوت‌کنندگان و سایر مقامات ورزشی | تهیه‌کنندگان و کارگردانان | مدیران استعداد | مدیران برنامه‌ریزی رسانه | گویندگان رادیو و تلویزیون و دی‌جی‌های رادیو | معلمان هنر، نمایش و موسیقی، پس از متوسطه | معلمان آموزش‌های تکمیلی | کارگران تفریحی | هنرمندان و انیماتورهای جلوه‌های ویژه | طراحان صحنه و نمایشگاه | نمایندگان و مدیران تجاری هنرمندان، مجریان و ورزشکاران | مدیران فنی رسانه</t>
+          <t>بازیگران | رقصندگان | طراحان رقص | نوازندگان و خوانندگان | مدیران موسیقی و آهنگسازان | دی‌جی‌ها، به جز رادیو | ورزشکاران و رقبای ورزشی | مربیان و استعدادیاب‌ها | داوران، قضاوت‌کنندگان و سایر مقامات ورزشی | تهیه‌کنندگان و کارگردانان | مدیران استعداد | مدیران برنامه‌ریزی رسانه | گویندگان رادیو و تلویزیون و دی‌جی‌های رادیو | مدرسان هنر، نمایش و موسیقی، آموزش عالی | معلمان خودسازی | کارکنان تفریحات | هنرمندان جلوه‌های ویژه و انیماتورها | طراحان صحنه و نمایشگاه | نمایندگان و مدیران تجاری هنرمندان، اجراکنندگان و ورزشکاران | مدیران/کارگردانان فنی رسانه</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Broadcast Announcers and Radio Disc Jockeys (گویندگان رادیو و تلویزیون و دی‌جی‌های رادیو)</t>
+          <t>گویندگان رادیو و تلویزیون و دی‌جی‌های رادیو (Broadcast Announcers and Radio Disc Jockeys)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -674,32 +674,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Adobe Audition | Audion Laboratories VoxPro | Avid Technology Pro Tools | نرم‌افزار سیستم اتاق خبر Burli | سیستم‌های رسانه دیجیتال Dalet Media Life | نرم‌افزار پایگاه داده | نرم‌افزار یکپارچه‌سازی برنامه‌های سازمانی EAI | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار ثبت برنامه | نرم‌افزار پردازش آماری | نرم‌افزار مرورگر وب | Zoom</t>
+          <t>Adobe Audition | Audion Laboratories VoxPro | Avid Technology Pro Tools | نرم‌افزار سیستم اتاق خبر Burli | سیستم‌های رسانه دیجیتال Dalet Media Life | نرم‌افزار پایگاه داده | نرم‌افزار یکپارچه‌سازی برنامه‌های کاربردی سازمانی EAI | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار ثبت برنامه | نرم‌افزار پردازش آماری | نرم‌افزار مرورگر وب | Zoom</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>صحبت کردن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نوشتن | یادگیری فعال | نظارت</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ارتباطات و رسانه | زبان انگلیسی | کامپیوتر و الکترونیک | مخابرات</t>
+          <t>ارتباطات و رسانه | زبان انگلیسی | رایانه و الکترونیک | مخابرات</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>بیان شفاهی | وضوح گفتار | درک شنیداری | تشخیص گفتار | درک نوشتاری | بیان نوشتاری | خلاقیت | روانی ایده‌ها | توجه انتخابی | استدلال قیاسی | استدلال استقرایی | دید نزدیک | نظم‌دهی اطلاعات | حساسیت به مسئله | اشتراک زمانی | سرعت بستن | حافظه‌سپاری | انعطاف‌پذیری دسته‌بندی</t>
+          <t>بیان شفاهی | وضوح گفتار | درک شفاهی | تشخیص گفتار | درک کتبی | بیان کتبی | اصالت | روانی ایده‌ها | توجه انتخابی | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | ترتیب‌دهی اطلاعات | حساسیت به مسئله | تقسیم توجه | سرعت بستار | حفظ کردن | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ایمیل | فشار زمانی | محیط داخلی، دارای کنترل محیطی | بحث‌های رودررو با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه یا تیم کاری | مکالمات تلفنی | فراوانی تصمیم‌گیری | تماس با دیگران | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | آزادی در تصمیم‌گیری | اهمیت دقیق یا صحیح بودن | صرف زمان برای نشستن | سخنرانی عمومی | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | سطح رقابت | قرار گرفتن در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | نامه‌ها و یادداشت‌های کتبی</t>
+          <t>ایمیل | فشار زمانی | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | فراوانی تصمیم‌گیری | ارتباط با دیگران | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | صرف زمان برای نشستن | سخنرانی عمومی | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سطح رقابت | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | نامه‌ها و یادداشت‌های کتبی</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>بازیگران | نمایندگان فروش تبلیغات | مدیران تبلیغات و ترویج | نمایندگان و مدیران تجاری هنرمندان، مجریان و ورزشکاران | تکنسین‌های صوتی و تصویری | نصاب‌ها و تعمیرکاران تجهیزات صوتی و تصویری | تکنسین‌های پخش | اپراتورهای دوربین، تلویزیون، ویدئو و فیلم | دی‌جی‌ها، به جز رادیو | ویراستاران | تدوینگران فیلم و ویدئو | مدیران برنامه‌ریزی رسانه | مدیران فنی رسانه | تحلیلگران اخبار، گزارشگران و روزنامه‌نگاران | شاعران، ترانه‌سرایان و نویسندگان خلاق | تهیه‌کنندگان و کارگردانان | متخصصان روابط عمومی | هنرمندان و انیماتورهای جلوه‌های ویژه | مدیران استعداد | نویسندگان و مؤلفان</t>
+          <t>بازیگران | نمایندگان فروش تبلیغات | مدیران تبلیغات و ترویج | نمایندگان و مدیران تجاری هنرمندان، اجراکنندگان و ورزشکاران | تکنسین‌های صوتی و تصویری | نصب‌کنندگان و تعمیرکنندگان تجهیزات صوتی و تصویری | تکنسین‌های پخش | اپراتورهای دوربین، تلویزیون، ویدئو و فیلم | دی‌جی‌ها، به جز رادیو | ویراستاران | تدوینگران فیلم و ویدئو | مدیران برنامه‌ریزی رسانه | مدیران/کارگردانان فنی رسانه | تحلیلگران اخبار، گزارشگران و روزنامه‌نگاران | شاعران، ترانه‌سرایان و نویسندگان خلاق | تهیه‌کنندگان و کارگردانان | متخصصان روابط عمومی | هنرمندان جلوه‌های ویژه و انیماتورها | مدیران استعداد | نویسندگان و مؤلفان</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>News Analysts, Reporters, and Journalists (تحلیلگران اخبار، گزارشگران و روزنامه‌نگاران)</t>
+          <t>تحلیلگران اخبار، گزارشگران و روزنامه‌نگاران (News Analysts, Reporters, and Journalists)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -731,32 +731,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Adobe After Effects | Adobe InDesign | Adobe Photoshop | Adobe Premiere Pro | Apple Final Cut Pro | Audion Laboratories VoxPro | Avid Technology Pro Tools | سیستم اتاق خبر Desktop Technologies NewsBoss | ESRI ArcView | Facebook | FileMaker Pro | Grass Valley EDIUS | زبان نشانه‌گذاری ابرمتن HTML | IBM SPSS Statistics | LexisNexis | نرم‌افزار نقشه‌برداری | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft SQL Server | Microsoft Visual FoxPro | Microsoft Word | Nielsen Arianna | Nielsen Marketbreaks | پایگاه‌های داده آنلاین | QuarkXPress | RCS NexGen Digital | Snapchat | سایت‌های رسانه‌های اجتماعی | نرم‌افزار رسانه‌های اجتماعی | نرم‌افزار تحلیل آماری | پایگاه‌های داده آماری | Twitter | نرم‌افزار ویرایش ویدئو | نرم‌افزار مرورگر وب | نرم‌افزار سیستم مدیریت محتوای وب CMS | WordPress | YouTube</t>
+          <t>Adobe After Effects | Adobe InDesign | Adobe Photoshop | Adobe Premiere Pro | Apple Final Cut Pro | Audion Laboratories VoxPro | Avid Technology Pro Tools | سیستم اتاق خبر Desktop Technologies NewsBoss | ESRI ArcView | Facebook | FileMaker Pro | Grass Valley EDIUS | زبان نشانه‌گذاری ابرمتن HTML | IBM SPSS Statistics | LexisNexis | نرم‌افزار نقشه‌برداری | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft SQL Server | Microsoft Visual FoxPro | Microsoft Word | Nielsen Arianna | Nielsen Marketbreaks | پایگاه‌های داده آنلاین | QuarkXPress | RCS NexGen Digital | Snapchat | سایت‌های رسانه‌های اجتماعی | نرم‌افزار رسانه‌های اجتماعی | نرم‌افزار تحلیل آماری | پایگاه‌های داده آماری | Twitter | نرم‌افزار ویرایش ویدیو | نرم‌افزار مرورگر وب | نرم‌افزار سیستم مدیریت محتوای وب CMS | WordPress | YouTube</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>صحبت کردن | درک مطلب | نوشتن | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | نظارت</t>
+          <t>سخن گفتن | درک مطلب | نگارش | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | ارتباطات و رسانه | قانون و دولت | کامپیوتر و الکترونیک | مخابرات | خدمات مشتری و شخصی | جغرافیا</t>
+          <t>زبان انگلیسی | ارتباطات و رسانه | قانون و دولت | رایانه و الکترونیک | مخابرات | خدمات مشتری و شخصی | جغرافیا</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شنیداری | بیان نوشتاری | وضوح گفتار | درک نوشتاری | تشخیص گفتار | دید نزدیک | نظم‌دهی اطلاعات | استدلال استقرایی | حساسیت به مسئله | توجه انتخابی | استدلال قیاسی | روانی ایده‌ها | خلاقیت | دید دور | انعطاف‌پذیری بستن</t>
+          <t>بیان شفاهی | درک شفاهی | بیان کتبی | وضوح گفتار | درک کتبی | تشخیص گفتار | بینایی نزدیک | ترتیب‌دهی اطلاعات | استدلال استقرایی | حساسیت به مسئله | توجه انتخابی | استدلال قیاسی | روانی ایده‌ها | اصالت | بینایی دور | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>فشار زمانی | ایمیل | تماس با دیگران | آزادی در تصمیم‌گیری | اهمیت دقیق یا صحیح بودن | مکالمات تلفنی | بحث‌های رودررو با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل محیطی | فراوانی تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای نشستن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | سطح رقابت | کار با یا مشارکت در یک گروه یا تیم کاری | تعامل با مشتریان خارجی یا عموم مردم</t>
+          <t>فشار زمانی | ایمیل | ارتباط با دیگران | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | فراوانی تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای نشستن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | سطح رقابت | کار با یا مشارکت در یک گروه کاری یا تیم | تعامل با مشتریان خارجی یا عموم مردم</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>گویندگان رادیو و تلویزیون و دی‌جی‌های رادیو | تحلیلگران هوش تجاری | معلمان ارتباطات، پس از متوسطه | کارمندان مکاتبات | گزارشگران دادگاه و زیرنویس‌نویسان همزمان | ویراستاران | تدوینگران فیلم و ویدئو | مورخان | تحلیلگران اطلاعات | مدیران برنامه‌ریزی رسانه | مدیران فنی رسانه | شاعران، ترانه‌سرایان و نویسندگان خلاق | دانشمندان علوم سیاسی | تهیه‌کنندگان و کارگردانان | مصححان و نشان‌گذاران کپی | متخصصان روابط عمومی | دستیاران تحقیقات علوم اجتماعی | جامعه‌شناسان | نویسندگان فنی | نویسندگان و مؤلفان</t>
+          <t>گویندگان رادیو و تلویزیون و دی‌جی‌های رادیو | تحلیلگران هوش تجاری | مدرسان ارتباطات، آموزش عالی | کارمندان مکاتبات | گزارشگران دادگاه و زیرنویس‌نویسان همزمان | ویراستاران | تدوینگران فیلم و ویدئو | مورخان | تحلیلگران اطلاعاتی | مدیران برنامه‌ریزی رسانه | مدیران/کارگردانان فنی رسانه | شاعران، ترانه‌سرایان و نویسندگان خلاق | دانشمندان علوم سیاسی | تهیه‌کنندگان و کارگردانان | مصححان و نشانه‌گذاران کپی | متخصصان روابط عمومی | دستیاران تحقیقات علوم اجتماعی | جامعه‌شناسان | نویسندگان فنی | نویسندگان و مؤلفان</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Public Relations Specialists (متخصصان روابط عمومی)</t>
+          <t>متخصصان روابط عمومی (Public Relations Specialists)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -788,32 +788,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>برنامه 3M Post-it | Adobe Acrobat | Adobe Acrobat Reader | Adobe Acrobat Writer | Adobe ActionScript | Adobe After Effects | نرم‌افزار Adobe Creative Cloud | Adobe Dreamweaver | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Airtable | Apple Final Cut Express | Apple Final Cut Pro | Apple Keynote | Apple QuickTime | Apple iPhoto | Apple macOS | Blackbaud The Raiser's Edge | نرم‌افزار وبلاگ‌نویسی | Canva | برگه‌های سبک آبشاری CSS | Cisco Webex | Cision CisionPoint | Drupal | زبان نشانه‌گذاری ابرمتن پویا DHTML | زبان نشانه‌گذاری ابرمتن توسعه‌پذیر XHTML | Facebook | FileMaker Pro | Google | Google Ads | Google Analytics | Google Docs | Google Drive | Google Slides | نرم‌افزار HubSpot | زبان نشانه‌گذاری ابرمتن HTML | Instagram | JamBoard | JavaScript | LexisNexis | LinkedIn | LogMeIn GoToWebinar | اتوماسیون بازاریابی Marketo | Mentimeter | Microsoft Dynamics | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SharePoint | Microsoft Word | Myspace | Nearpod | Oracle Business Intelligence Discoverer | Oracle Eloqua | ParentSquare | نرم‌افزار پادکست | نرم‌افزار Salesforce | نرم‌افزار تعاملی Slido | SmugMug Flickr | سایت‌های رسانه‌های اجتماعی | Twitter | نرم‌افزار مرورگر وب | نرم‌افزار مدیریت وب‌سایت | Wireshark | WordPress | YouTube</t>
+          <t>3M Post-it App | Adobe Acrobat | Adobe Acrobat Reader | Adobe Acrobat Writer | Adobe ActionScript | Adobe After Effects | نرم‌افزار Adobe Creative Cloud | Adobe Dreamweaver | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Airtable | Apple Final Cut Express | Apple Final Cut Pro | Apple Keynote | Apple QuickTime | Apple iPhoto | Apple macOS | Blackbaud The Raiser's Edge | نرم‌افزار وبلاگ‌نویسی | Canva | برگه‌های سبک آبشاری CSS | Cisco Webex | Cision CisionPoint | Drupal | زبان نشانه‌گذاری ابرمتن پویا DHTML | زبان نشانه‌گذاری ابرمتن توسعه‌پذیر XHTML | Facebook | FileMaker Pro | Google | Google Ads | Google Analytics | Google Docs | Google Drive | Google Slides | نرم‌افزار HubSpot | زبان نشانه‌گذاری ابرمتن HTML | Instagram | JamBoard | JavaScript | LexisNexis | LinkedIn | LogMeIn GoToWebinar | Marketo Marketing Automation | Mentimeter | Microsoft Dynamics | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SharePoint | Microsoft Word | Myspace | Nearpod | Oracle Business Intelligence Discoverer | Oracle Eloqua | ParentSquare | نرم‌افزار پادکست | نرم‌افزار Salesforce | نرم‌افزار تعاملی Slido | SmugMug Flickr | سایت‌های رسانه‌های اجتماعی | Twitter | نرم‌افزار مرورگر وب | نرم‌افزار مدیریت وب‌سایت | Wireshark | WordPress | YouTube</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | صحبت کردن | درک مطلب | نوشتن | تفکر انتقادی | یادگیری فعال | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ارتباطات و رسانه | زبان انگلیسی | خدمات مشتری و شخصی | مدیریت و اداره | فروش و بازاریابی | کامپیوتر و الکترونیک</t>
+          <t>ارتباطات و رسانه | زبان انگلیسی | خدمات مشتری و شخصی | مدیریت و اداره | فروش و بازاریابی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شنیداری | بیان شفاهی | بیان نوشتاری | تشخیص گفتار | وضوح گفتار | درک نوشتاری | حساسیت به مسئله | استدلال قیاسی | روانی ایده‌ها | خلاقیت | استدلال استقرایی | دید نزدیک | انعطاف‌پذیری دسته‌بندی | نظم‌دهی اطلاعات</t>
+          <t>درک شفاهی | بیان شفاهی | بیان کتبی | تشخیص گفتار | وضوح گفتار | درک کتبی | حساسیت به مسئله | استدلال قیاسی | روانی ایده‌ها | اصالت | استدلال استقرایی | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های رودررو با افراد و درون تیم‌ها | مکالمات تلفنی | فشار زمانی | کار با یا مشارکت در یک گروه یا تیم کاری | تماس با دیگران | محیط داخلی، دارای کنترل محیطی | اهمیت دقیق یا صحیح بودن | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای نشستن | سطح رقابت | آزادی در تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | نتایج کاری و خروجی‌های سایر کارگران</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | فشار زمانی | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای نشستن | سطح رقابت | آزادی در تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | پیامدهای کاری و نتایج سایر کارکنان</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>نمایندگان فروش تبلیغات | مدیران تبلیغات و ترویج | نمایندگان و مدیران تجاری هنرمندان، مجریان و ورزشکاران | معلمان کسب‌وکار، پس از متوسطه | مدیران ارشد اجرایی | معلمان ارتباطات، پس از متوسطه | منشی‌های اجرایی و دستیاران اداری اجرایی | جمع‌آوری‌کنندگان کمک مالی | مدیران جمع‌آوری کمک مالی | تحلیلگران مدیریت | تحلیلگران تحقیقات بازار و متخصصان بازاریابی | مدیران بازاریابی | مدیران برنامه‌ریزی رسانه | برنامه‌ریزان جلسات، همایش‌ها و رویدادها | مدیران روابط عمومی | مدیران فروش | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و مسافرتی | استراتژیست‌های بازاریابی جستجو | بازاریابان تلفنی | نویسندگان و مؤلفان</t>
+          <t>نمایندگان فروش تبلیغات | مدیران تبلیغات و ترویج | نمایندگان و مدیران تجاری هنرمندان، اجراکنندگان و ورزشکاران | اساتید کسب‌وکار، پس از متوسطه | مدیران ارشد اجرایی | مدرسان ارتباطات، آموزش عالی | منشی‌های اجرایی و دستیاران اداری اجرایی | جمع‌آوری‌کنندگان کمک مالی | مدیران جمع‌آوری کمک‌های مالی | تحلیل‌گران مدیریت | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | مدیران بازاریابی | مدیران برنامه‌ریزی رسانه | برنامه‌ریزان جلسات، همایش‌ها و رویدادها | مدیران روابط عمومی | مدیران فروش | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | استراتژیست‌های بازاریابی جستجو | بازاریابان تلفنی | نویسندگان و مؤلفان</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Editors (ویراستاران)</t>
+          <t>ویراستاران (Editors)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -850,27 +850,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | نوشتن | گوش دادن فعال | تفکر انتقادی | صحبت کردن | یادگیری فعال | نظارت</t>
+          <t>درک مطلب | نگارش | گوش دادن فعال | تفکر انتقادی | سخن گفتن | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | ارتباطات و رسانه | مدیریت و اداره | اداری | آموزش و پرورش | خدمات مشتری و شخصی | کامپیوتر و الکترونیک</t>
+          <t>زبان انگلیسی | ارتباطات و رسانه | مدیریت و اداره | اداری | آموزش و پرورش | خدمات مشتری و شخصی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک نوشتاری | بیان نوشتاری | درک شنیداری | بیان شفاهی | روانی ایده‌ها | دید نزدیک | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | خلاقیت | استدلال قیاسی | نظم‌دهی اطلاعات | استدلال استقرایی | حساسیت به مسئله | انعطاف‌پذیری بستن | توجه انتخابی</t>
+          <t>درک کتبی | بیان کتبی | درک شفاهی | بیان شفاهی | روانی ایده‌ها | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | اصالت | استدلال قیاسی | ترتیب‌دهی اطلاعات | استدلال استقرایی | حساسیت به مسئله | انعطاف‌پذیری بستار | توجه انتخابی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>محیط داخلی، دارای کنترل محیطی | ایمیل | بحث‌های رودررو با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه یا تیم کاری | فشار زمانی | تماس با دیگران | مکالمات تلفنی | اهمیت دقیق یا صحیح بودن | صرف زمان برای نشستن | فراوانی تصمیم‌گیری | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | اهمیت تکرار وظایف مشابه | تعامل با مشتریان خارجی یا عموم مردم</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | ارتباط با دیگران | مکالمات تلفنی | اهمیت دقیق یا درست بودن | صرف زمان برای نشستن | فراوانی تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | اهمیت تکرار وظایف یکسان | تعامل با مشتریان خارجی یا عموم مردم</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مدیران هنری | ناشران دسکتاپ | متخصصان مدیریت اسناد | تدوینگران فیلم و ویدئو | طراحان گرافیک | کتابداران و متخصصان مجموعه‌های رسانه‌ای | معلمان علوم کتابداری، پس از متوسطه | تکنسین‌های کتابخانه | تحلیلگران مدیریت | مدیران برنامه‌ریزی رسانه | مدیران فنی رسانه | تحلیلگران اخبار، گزارشگران و روزنامه‌نگاران | شاعران، ترانه‌سرایان و نویسندگان خلاق | تهیه‌کنندگان و کارگردانان | مصححان و نشان‌گذاران کپی | متخصصان روابط عمومی | نویسندگان فنی | مدیران وب | طراحان وب و رابط دیجیتال | نویسندگان و مؤلفان</t>
+          <t>مدیران هنری | ناشران رومیزی | متخصصان مدیریت اسناد | تدوینگران فیلم و ویدئو | طراحان گرافیک | کتابداران و متخصصان مجموعه‌های رسانه‌ای | مدرسان علوم کتابداری، آموزش عالی | تکنسین‌های کتابخانه | تحلیل‌گران مدیریت | مدیران برنامه‌ریزی رسانه | مدیران/کارگردانان فنی رسانه | تحلیلگران اخبار، گزارشگران و روزنامه‌نگاران | شاعران، ترانه‌سرایان و نویسندگان خلاق | تهیه‌کنندگان و کارگردانان | مصححان و نشانه‌گذاران کپی | متخصصان روابط عمومی | نویسندگان فنی | مدیران وب | طراحان رابط دیجیتال و وب | نویسندگان و مؤلفان</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Technical Writers (نویسندگان فنی)</t>
+          <t>نویسندگان فنی (Technical Writers)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -902,32 +902,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Adobe Acrobat | Adobe Captivate | نرم‌افزار Adobe Creative Cloud | Adobe Dreamweaver | Adobe FrameMaker | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Adobe RoboHelp | Apple Final Cut Pro | Atlassian Confluence | Atlassian JIRA | Author-it | Autodesk AutoCAD | Blink | برگه‌های سبک آبشاری CSS | مجموعه گرافیکی Corel CorelDraw | Corel Paint Shop Pro | Corel Ventura | معماری تایپ اطلاعات داروین DITA | Dassault Systemes CATIA | Dassault Systemes SolidWorks | Drupal | زبان نشانه‌گذاری ابرمتن پویا DHTML | Epic Systems | زبان نشانه‌گذاری ابرمتن توسعه‌پذیر XHTML | زبان نشانه‌گذاری توسعه‌پذیر XML | FileMaker Pro | Git | GitHub | Google Sites | زبان نشانه‌گذاری ابرمتن HTML | IBM Cognos Business Intelligence | IBM Notes | IBM Rational ClearCase | IBM Rational ClearQuest | JavaScript | JustSystems XMetaL | MadCap Software MadCap Flare | Microsoft ASP.NET | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SQL Server | خدمات گزارش‌دهی Microsoft SQL Server SSRS | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Word | Objective C | Oracle Business Intelligence Discoverer | Oracle E-Business Suite Financials | Oracle Java | صفحات سرور جاوا Oracle JavaServer Pages JSP | PHP | PTC Arbortext | PTC Creo Parametric | ParentSquare | نرم‌افزار Perforce Helix | Quadralay WebWorks ePublisher | SAP Business Objects | SAP Crystal Reports | SAS | زبان نشانه‌گذاری عمومی استاندارد شده SGML | زبان پرس‌وجوی ساختاریافته SQL | Talisma Knowledgebase | نرم‌افزار مرورگر وب</t>
+          <t>Adobe Acrobat | Adobe Captivate | نرم‌افزار Adobe Creative Cloud | Adobe Dreamweaver | Adobe FrameMaker | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Adobe RoboHelp | Apple Final Cut Pro | Atlassian Confluence | Atlassian JIRA | Author-it | Autodesk AutoCAD | Blink | برگه‌های سبک آبشاری CSS | Corel CorelDraw Graphics Suite | Corel Paint Shop Pro | Corel Ventura | معماری تایپ اطلاعات داروین DITA | Dassault Systemes CATIA | Dassault Systemes SolidWorks | Drupal | زبان نشانه‌گذاری ابرمتن پویا DHTML | Epic Systems | زبان نشانه‌گذاری ابرمتن توسعه‌پذیر XHTML | زبان نشانه‌گذاری توسعه‌پذیر XML | FileMaker Pro | Git | GitHub | Google Sites | زبان نشانه‌گذاری ابرمتن HTML | IBM Cognos Business Intelligence | IBM Notes | IBM Rational ClearCase | IBM Rational ClearQuest | JavaScript | JustSystems XMetaL | MadCap Software MadCap Flare | Microsoft ASP.NET | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SQL Server | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Word | Objective C | Oracle Business Intelligence Discoverer | Oracle E-Business Suite Financials | Oracle Java | Oracle JavaServer Pages JSP | PHP | PTC Arbortext | PTC Creo Parametric | ParentSquare | نرم‌افزار Perforce Helix | Quadralay WebWorks ePublisher | SAP Business Objects | SAP Crystal Reports | SAS | Standardized general markup language SGML | زبان پرس‌وجوی ساختاریافته SQL | Talisma Knowledgebase | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>نوشتن | درک مطلب | گوش دادن فعال | صحبت کردن | تفکر انتقادی | یادگیری فعال | نظارت</t>
+          <t>نگارش | درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | کامپیوتر و الکترونیک | اداری | ارتباطات و رسانه | مدیریت و اداره | ایمنی و امنیت عمومی | آموزش و پرورش | تولید و پردازش</t>
+          <t>زبان انگلیسی | رایانه و الکترونیک | اداری | ارتباطات و رسانه | مدیریت و اداره | ایمنی و امنیت عمومی | آموزش و پرورش | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>بیان نوشتاری | درک نوشتاری | دید نزدیک | درک شنیداری | بیان شفاهی | استدلال قیاسی | نظم‌دهی اطلاعات | حساسیت به مسئله | وضوح گفتار | استدلال استقرایی | تشخیص گفتار | تجسم | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها</t>
+          <t>بیان کتبی | درک کتبی | بینایی نزدیک | درک شفاهی | بیان شفاهی | استدلال قیاسی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | وضوح گفتار | استدلال استقرایی | تشخیص گفتار | تجسم | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ایمیل | کار با یا مشارکت در یک گروه یا تیم کاری | اهمیت دقیق یا صحیح بودن | صرف زمان برای نشستن | اهمیت تکرار وظایف مشابه | آزادی در تصمیم‌گیری | بحث‌های رودررو با افراد و درون تیم‌ها | فشار زمانی | محیط داخلی، دارای کنترل محیطی | مکالمات تلفنی | تماس با دیگران | صرف زمان برای انجام حرکات تکراری | فراوانی تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای استفاده از دست‌ها جهت کنترل، لمس یا کار با اشیاء، ابزارها یا کنترل‌ها</t>
+          <t>ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | صرف زمان برای نشستن | اهمیت تکرار وظایف یکسان | آزادی در تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فشار زمانی | محیط داخلی، دارای کنترل شرایط محیطی | مکالمات تلفنی | ارتباط با دیگران | صرف زمان برای انجام حرکات تکراری | فراوانی تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مدیران داده‌های بالینی | برنامه‌نویسان کامپیوتر | تحلیلگران سیستم‌های کامپیوتری | مهندسان/معماران سیستم‌های کامپیوتری | کارمندان مکاتبات | دانشمندان داده | مدیران پایگاه داده | متخصصان مدیریت اسناد | ویراستاران | نقشه‌کشان برق و الکترونیک | مهندسان صنایع | مدیران پروژه فناوری اطلاعات | تحلیلگران مدیریت | متخصصان مدیریت پروژه | مصححان و نشان‌گذاران کپی | دستیاران تحقیقات علوم اجتماعی | توسعه‌دهندگان نرم‌افزار | دستیاران آماری | طراحان وب و رابط دیجیتال | نویسندگان و مؤلفان</t>
+          <t>مدیران داده‌های بالینی | برنامه‌نویسان کامپیوتر | تحلیلگران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | کارمندان مکاتبات | دانشمندان داده | مدیران پایگاه داده | متخصصان مدیریت اسناد | ویراستاران | نقشه‌کشان برق و الکترونیک | مهندسان صنایع | مدیران پروژه فناوری اطلاعات | تحلیل‌گران مدیریت | متخصصان مدیریت پروژه | مصححان و نشانه‌گذاران کپی | دستیاران تحقیقات علوم اجتماعی | توسعه‌دهندگان نرم‌افزار | دستیاران آماری | طراحان رابط دیجیتال و وب | نویسندگان و مؤلفان</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Writers and Authors (نویسندگان و مؤلفان)</t>
+          <t>نویسندگان و مؤلفان (Writers and Authors)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -964,27 +964,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>نوشتن | درک مطلب | گوش دادن فعال | صحبت کردن | تفکر انتقادی | یادگیری فعال | نظارت</t>
+          <t>نگارش | درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>فروش و بازاریابی | ارتباطات و رسانه | خدمات مشتری و شخصی | کامپیوتر و الکترونیک</t>
+          <t>فروش و بازاریابی | ارتباطات و رسانه | خدمات مشتری و شخصی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بیان نوشتاری | درک نوشتاری | درک شنیداری | بیان شفاهی | روانی ایده‌ها | خلاقیت | تشخیص گفتار | وضوح گفتار | دید نزدیک | استدلال استقرایی | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | نظم‌دهی اطلاعات | حساسیت به مسئله</t>
+          <t>بیان کتبی | درک کتبی | درک شفاهی | بیان شفاهی | روانی ایده‌ها | اصالت | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | استدلال استقرایی | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ایمیل | تماس با دیگران | فشار زمانی | مکالمات تلفنی | فراوانی تصمیم‌گیری | بحث‌های رودررو با افراد و درون تیم‌ها | سطح رقابت | صرف زمان برای نشستن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا صحیح بودن | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | نامه‌ها و یادداشت‌های کتبی | تعامل با مشتریان خارجی یا عموم مردم | قرار گرفتن در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | کار با یا مشارکت در یک گروه یا تیم کاری | تعیین وظایف، اولویت‌ها و اهداف | نتایج کاری و خروجی‌های سایر کارگران | آزادی در تصمیم‌گیری</t>
+          <t>ایمیل | ارتباط با دیگران | فشار زمانی | مکالمات تلفنی | فراوانی تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سطح رقابت | صرف زمان برای نشستن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا درست بودن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نامه‌ها و یادداشت‌های کتبی | تعامل با مشتریان خارجی یا عموم مردم | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | پیامدهای کاری و نتایج سایر کارکنان | آزادی در تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>نمایندگان فروش تبلیغات | مدیران تبلیغات و ترویج | نمایندگان و مدیران تجاری هنرمندان، مجریان و ورزشکاران | مدیران هنری | ویراستاران | طراحان گرافیک | تحلیلگران تحقیقات بازار و متخصصان بازاریابی | مدیران بازاریابی | مدیران برنامه‌ریزی رسانه | تحلیلگران اخبار، گزارشگران و روزنامه‌نگاران | شاعران، ترانه‌سرایان و نویسندگان خلاق | تهیه‌کنندگان و کارگردانان | مصححان و نشان‌گذاران کپی | مدیران روابط عمومی | متخصصان روابط عمومی | استراتژیست‌های بازاریابی جستجو | هنرمندان و انیماتورهای جلوه‌های ویژه | مدیران استعداد | نویسندگان فنی | طراحان وب و رابط دیجیتال</t>
+          <t>نمایندگان فروش تبلیغات | مدیران تبلیغات و ترویج | نمایندگان و مدیران تجاری هنرمندان، اجراکنندگان و ورزشکاران | مدیران هنری | ویراستاران | طراحان گرافیک | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | مدیران بازاریابی | مدیران برنامه‌ریزی رسانه | تحلیلگران اخبار، گزارشگران و روزنامه‌نگاران | شاعران، ترانه‌سرایان و نویسندگان خلاق | تهیه‌کنندگان و کارگردانان | مصححان و نشانه‌گذاران کپی | مدیران روابط عمومی | متخصصان روابط عمومی | استراتژیست‌های بازاریابی جستجو | هنرمندان جلوه‌های ویژه و انیماتورها | مدیران استعداد | نویسندگان فنی | طراحان رابط دیجیتال و وب</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Poets, Lyricists and Creative Writers (شاعران، ترانه‌سرایان و نویسندگان خلاق)</t>
+          <t>شاعران، ترانه‌سرایان و نویسندگان خلاق (Poets, Lyricists and Creative Writers)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1016,32 +1016,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Adobe Acrobat | نرم‌افزار Adobe Creative Cloud | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Apple iWork Pages | نرم‌افزار Ashley Software Writer's Blocks | نرم‌افزار ویرایش AutoCrit Editing Wizard | Bare Bones Software BBEdit | Blogger | Contour Storyteller | Facebook | Google Drive | Literature &amp; Latte Scrivener | MasterWriter | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Word | OpenOffice.org | Power Structure | Ravenshead Services WriteItNow | Red Sweater MarsEdit | RoughDraft | ScriptPerfection Power Writer | Skype | نرم‌افزار رسانه‌های اجتماعی | Storymind StoryWeaver | نرم‌افزار تبدیل متن به گفتار | Tumblr | WhiteSmoke | WordPress | Write Brothers Dramatica | WriteWay Pro | YouTube</t>
+          <t>Adobe Acrobat | نرم‌افزار Adobe Creative Cloud | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Apple iWork Pages | نرم‌افزار Ashley Software Writer's Blocks | AutoCrit Editing Wizard | Bare Bones Software BBEdit | Blogger | Contour Storyteller | Facebook | Google Drive | Literature &amp; Latte Scrivener | MasterWriter | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Word | OpenOffice.org | Power Structure | Ravenshead Services WriteItNow | Red Sweater MarsEdit | RoughDraft | ScriptPerfection Power Writer | Skype | نرم‌افزار رسانه‌های اجتماعی | Storymind StoryWeaver | نرم‌افزار تبدیل متن به گفتار | Tumblr | WhiteSmoke | WordPress | Write Brothers Dramatica | WriteWay Pro | YouTube</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>نوشتن | درک مطلب | صحبت کردن | تفکر انتقادی | یادگیری فعال | گوش دادن فعال</t>
+          <t>نگارش | درک مطلب | سخن گفتن | تفکر انتقادی | یادگیری فعال | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | ارتباطات و رسانه | کامپیوتر و الکترونیک | اداری | فروش و بازاریابی | هنرهای زیبا</t>
+          <t>زبان انگلیسی | ارتباطات و رسانه | رایانه و الکترونیک | اداری | فروش و بازاریابی | هنرهای زیبا</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>بیان نوشتاری | روانی ایده‌ها | درک نوشتاری | خلاقیت | درک شنیداری | دید نزدیک | بیان شفاهی | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | نظم‌دهی اطلاعات | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | توجه انتخابی</t>
+          <t>بیان کتبی | روانی ایده‌ها | درک کتبی | اصالت | درک شفاهی | بینایی نزدیک | بیان شفاهی | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | توجه انتخابی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای نشستن | آزادی در تصمیم‌گیری | ایمیل | سطح رقابت | اهمیت تکرار وظایف مشابه | اهمیت دقیق یا صحیح بودن</t>
+          <t>تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای نشستن | آزادی در تصمیم‌گیری | ایمیل | سطح رقابت | اهمیت تکرار وظایف یکسان | اهمیت دقیق یا درست بودن</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>بازیگران | مدیران هنری | معلمان هنر، نمایش و موسیقی، پس از متوسطه | گویندگان رادیو و تلویزیون و دی‌جی‌های رادیو | متصدیان | ویراستاران | معلمان زبان و ادبیات انگلیسی، پس از متوسطه | تدوینگران فیلم و ویدئو | هنرمندان تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | طراحان گرافیک | مورخان | مدیران موسیقی و آهنگسازان | تحلیلگران اخبار، گزارشگران و روزنامه‌نگاران | تهیه‌کنندگان و کارگردانان | مصححان و نشان‌گذاران کپی | متخصصان روابط عمومی | هنرمندان و انیماتورهای جلوه‌های ویژه | مدیران استعداد | نویسندگان فنی | نویسندگان و مؤلفان</t>
+          <t>بازیگران | مدیران هنری | مدرسان هنر، نمایش و موسیقی، آموزش عالی | گویندگان رادیو و تلویزیون و دی‌جی‌های رادیو | موزه‌داران | ویراستاران | مدرسان زبان و ادبیات انگلیسی، آموزش عالی | تدوینگران فیلم و ویدئو | هنرمندان تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | طراحان گرافیک | مورخان | مدیران موسیقی و آهنگسازان | تحلیلگران اخبار، گزارشگران و روزنامه‌نگاران | تهیه‌کنندگان و کارگردانان | مصححان و نشانه‌گذاران کپی | متخصصان روابط عمومی | هنرمندان جلوه‌های ویژه و انیماتورها | مدیران استعداد | نویسندگان فنی | نویسندگان و مؤلفان</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0040_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0040_fa.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | نظارت | درک مطلب | تفکر انتقادی</t>
+          <t>سخن گفتن | گوش دادن فعال | نظارت | درک مطلب | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت شنوایی | به خاطرسپاری | درک کتبی | تشخیص گفتار | توجه شنیداری | وضوح گفتار | دید نزدیک | ابتکار | سرعت درک الگو | چابکی انگشتان | چابکی دستی | انعطاف‌پذیری درک الگو | بیان کتبی | ثبات دست و بازو | سرعت ادراک | مرتب‌سازی اطلاعات | روانی ایده‌ها</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت شنوایی | حفظ کردن | درک کتبی | تشخیص گفتار | توجه شنیداری | وضوح گفتار | بینایی نزدیک | اصالت | سرعت بستار | مهارت انگشتان | مهارت دستی | انعطاف‌پذیری بستار | بیان کتبی | ثبات دست و بازو | سرعت ادراکی | ترتیب‌دهی اطلاعات | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>بازیگران | استادان و مدرسان هنر، تئاتر و موسیقی در آموزش عالی | ورزشکاران و قهرمانان ورزشی | گویندگان پخش و مجریان رادیویی | طراحان حرکات موزون | رقصندگان | دی‌جی‌ها (به‌جز رادیو) | استادان و مدرسان زبان و ادبیات انگلیسی در آموزش عالی | هنرمندان هنرهای تجسمی شامل نقاشان، مجسمه‌سازان و تصویرگران | تاریخ‌دانان | معلمان دوره متوسطه اول (به‌جز استثنایی و فنی‌وحرفه‌ای) | مدیران موسیقی و آهنگسازان | موسیقی‌درمانگران | تعمیرکاران و کوک‌کنندگان سازهای موسیقی | شاعران، ترانه‌سرایان و نویسندگان خلاق | تهیه‌کنندگان و کارگردانان | معلمان دوره متوسطه دوم (به‌جز استثنایی و فنی‌وحرفه‌ای) | مدرسان دوره‌های آزاد و مهارت‌آموزی شخصی | تکنسین‌های صدابرداری و مهندسی صدا | مدیران جذب استعدادهای هنری</t>
+          <t>بازیگران | مدرسان هنرهای تجسمی، نمایشی و موسیقی در دانشگاه‌ها و مراکز آموزش عالی | ورزشکاران و قهرمانان حرفه‌ای | گویندگان پخش و مجریان رادیویی | طراحان حرکت و کوروگراف‌ها | هنرمندان رقص و حرکات موزون | دی‌جی‌ها (به‌جز رادیو) | مدرسان زبان و ادبیات انگلیسی در دانشگاه‌ها و مراکز آموزش عالی | هنرمندان هنرهای تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | مورخان | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | رهبران ارکستر، مدیران موسیقی و آهنگسازان | موسیقی‌درمانگران | تعمیرکاران و کوک‌کنندگان سازهای موسیقی | شاعران، ترانه‌سرایان و نویسندگان خلاق | تهیه‌کنندگان و کارگردانان | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان دوره‌های آزاد و مهارت‌آموزی فردی | تکنسین‌های مهندسی صدا | مسئولان انتخاب بازیگر و استعدادیابی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -560,22 +560,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Adobe Audition | Avid Technology Pro Tools | Audion Laboratories VoxPro | نرم‌افزار Microsoft Office | Microsoft Excel | Microsoft Word</t>
+          <t>Adobe Audition | Avid Technology Pro Tools | Audion Laboratories VoxPro | نرم‌افزار Microsoft Office | نرم‌افزار Microsoft Office | Microsoft Word</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>هنرهای زیبا | خدمات مشتریان و خدمات فردی | ارتباطات و رسانه | زبان انگلیسی | رایانه و الکترونیک | فروش و بازاریابی | مخابرات</t>
+          <t>هنرهای زیبا | خدمات مشتری و شخصی | ارتباطات و رسانه | زبان انگلیسی | رایانه و الکترونیک | فروش و بازاریابی | مخابرات</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | مرتب‌سازی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری طبقه‌بندی | تقسیم توجه | چابکی انگشتان | چابکی دستی | دید دور | به خاطرسپاری | روانی ایده‌ها | توجه شنیداری | ابتکار | حساسیت شنوایی | ثبات دست و بازو</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | مهارت انگشتان | مهارت دستی | بینایی دور | حفظ کردن | روانی ایده‌ها | توجه شنیداری | اصالت | حساسیت شنوایی | ثبات دست و بازو</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>نمایندگان و مدیران برنامه‌های هنرمندان و ورزشکاران | ورزشکاران و قهرمانان ورزشی | تکنسین‌های صوت و تصویر | نصابان و تعمیرکاران تجهیزات دیداری و شنیداری | گویندگان پخش و مجریان رادیویی | تکنسین‌های پخش | طراحان حرکات موزون | معرفی‌کنندگان و مروجان محصولات | تدوین‌گران فیلم و ویدئو | مهمانداران و میزبانان سالن‌های پذیرایی | مدیران پخش و برنامه‌ریزی رسانه | مدیران فنی رسانه | برنامه‌ریزان همایش‌ها، نشست‌ها و رویدادها | مدیران موسیقی و آهنگسازان | نوازندگان و خوانندگان | تهیه‌کنندگان و کارگردانان | تکنسین‌های صدابرداری و مهندسی صدا | هنرمندان جلوه‌های ویژه و پویانماها | مدیران جذب استعدادهای هنری | طراحان بازی‌های ویدیویی</t>
+          <t>مدیران برنامه‌ها و نمایندگان هنرمندان، مجریان و ورزشکاران | ورزشکاران و قهرمانان حرفه‌ای | تکنسین‌های تجهیزات صوتی و تصویری | نصاب و تعمیرکار تجهیزات صوتی و تصویری | گویندگان پخش و مجریان رادیویی | تکنسین‌های پخش و اتاق فرمان | طراحان حرکت و کوروگراف‌ها | معرفی‌کنندگان و مروجان کالا | تدوین‌گران فیلم و ویدیو | میزبانان رستوران، سالن پذیرایی و کافی‌شاپ | مدیران برنامه‌ریزی و پخش رسانه | مدیران فنی رسانه | کارشناسان برنامه‌ریزی و برگزاری همایش‌ها و رویدادها | رهبران ارکستر، مدیران موسیقی و آهنگسازان | نوازندگان و خوانندگان | تهیه‌کنندگان و کارگردانان | تکنسین‌های مهندسی صدا | پویانماها و طراحان جلوه‌های ویژه | مسئولان انتخاب بازیگر و استعدادیابی | طراحان بازی‌های ویدیویی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>هنرهای زیبا | ارتباطات و رسانه | زبان انگلیسی | خدمات مشتریان و خدمات فردی | فروش و بازاریابی | آموزش و پرورش | روان‌شناسی</t>
+          <t>هنرهای زیبا | ارتباطات و رسانه | زبان انگلیسی | خدمات مشتری و شخصی | فروش و بازاریابی | آموزش و پرورش | روان‌شناسی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | مرتب‌سازی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری طبقه‌بندی | تقسیم توجه | چابکی انگشتان | چابکی دستی | دید دور | به خاطرسپاری | روانی ایده‌ها | ابتکار | هماهنگی عمومی بدن | استقامت | تعادل عمومی بدن</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | مهارت انگشتان | مهارت دستی | بینایی دور | حفظ کردن | روانی ایده‌ها | اصالت | هماهنگی کلی بدن | استقامت | تعادل کلی بدن</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>بازیگران | رقصندگان | طراحان حرکات موزون | نوازندگان و خوانندگان | مدیران موسیقی و آهنگسازان | دی‌جی‌ها (به‌جز رادیو) | ورزشکاران و قهرمانان ورزشی | مربیان و استعدادیابان ورزشی | داوران و مسئولان مسابقات ورزشی | تهیه‌کنندگان و کارگردانان | مدیران جذب استعدادهای هنری | مدیران پخش و برنامه‌ریزی رسانه | گویندگان پخش و مجریان رادیویی | استادان و مدرسان هنر، تئاتر و موسیقی در آموزش عالی | مدرسان دوره‌های آزاد و مهارت‌آموزی شخصی | کارشناسان و مربیان امور تفریحی | هنرمندان جلوه‌های ویژه و پویانماها | طراحان صحنه و دکور | نمایندگان و مدیران برنامه‌های هنرمندان و ورزشکاران | مدیران فنی رسانه</t>
+          <t>بازیگران | هنرمندان رقص و حرکات موزون | طراحان حرکت و کوروگراف‌ها | نوازندگان و خوانندگان | رهبران ارکستر، مدیران موسیقی و آهنگسازان | دی‌جی‌ها (به‌جز رادیو) | ورزشکاران و قهرمانان حرفه‌ای | مربیان و استعدادیابان ورزشی | داوران و مسئولان مسابقات ورزشی | تهیه‌کنندگان و کارگردانان | مسئولان انتخاب بازیگر و استعدادیابی | مدیران برنامه‌ریزی و پخش رسانه | گویندگان پخش و مجریان رادیویی | مدرسان هنرهای تجسمی، نمایشی و موسیقی در دانشگاه‌ها و مراکز آموزش عالی | مربیان دوره‌های آزاد و مهارت‌آموزی فردی | کارکنان و متصدیان امور تفریحی و اوقات فراغت | پویانماها و طراحان جلوه‌های ویژه | طراحان صحنه و نمایشگاه | مدیران برنامه‌ها و نمایندگان هنرمندان، مجریان و ورزشکاران | مدیران فنی رسانه</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | نظارت</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>بیان شفاهی | وضوح گفتار | درک شفاهی | تشخیص گفتار | درک کتبی | بیان کتبی | ابتکار | روانی ایده‌ها | توجه انتخابی | استدلال قیاسی | استدلال استقرایی | دید نزدیک | مرتب‌سازی اطلاعات | حساسیت به مسئله | تقسیم توجه | سرعت درک الگو | به خاطرسپاری | انعطاف‌پذیری طبقه‌بندی</t>
+          <t>بیان شفاهی | وضوح گفتار | درک شفاهی | تشخیص گفتار | درک کتبی | بیان کتبی | اصالت | روانی ایده‌ها | توجه انتخابی | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | ترتیب‌دهی اطلاعات | حساسیت به مسئله | تقسیم توجه | سرعت بستار | حفظ کردن | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>بازیگران | کارشناسان فروش تبلیغات | مدیران تبلیغات و روابط عمومی | نمایندگان و مدیران برنامه‌های هنرمندان و ورزشکاران | تکنسین‌های صوت و تصویر | نصابان و تعمیرکاران تجهیزات دیداری و شنیداری | تکنسین‌های پخش | تصویربرداران تلویزیون، ویدئو و سینما | دی‌جی‌ها (به‌جز رادیو) | ویراستاران | تدوین‌گران فیلم و ویدئو | مدیران پخش و برنامه‌ریزی رسانه | مدیران فنی رسانه | تحلیل‌گران خبر، خبرنگاران و روزنامه‌نگاران | شاعران، ترانه‌سرایان و نویسندگان خلاق | تهیه‌کنندگان و کارگردانان | کارشناسان روابط عمومی | هنرمندان جلوه‌های ویژه و پویانماها | مدیران جذب استعدادهای هنری | نویسندگان و پدیدآورندگان</t>
+          <t>بازیگران | کارشناسان فروش فضاهای تبلیغاتی | مدیران تبلیغات و روابط ترویجی | مدیران برنامه‌ها و نمایندگان هنرمندان، مجریان و ورزشکاران | تکنسین‌های تجهیزات صوتی و تصویری | نصاب و تعمیرکار تجهیزات صوتی و تصویری | تکنسین‌های پخش و اتاق فرمان | تصویربرداران تلویزیون، ویدیو و سینما | دی‌جی‌ها (به‌جز رادیو) | ویراستاران | تدوین‌گران فیلم و ویدیو | مدیران برنامه‌ریزی و پخش رسانه | مدیران فنی رسانه | تحلیل‌گران خبر، خبرنگاران و روزنامه‌نگاران | شاعران، ترانه‌سرایان و نویسندگان خلاق | تهیه‌کنندگان و کارگردانان | کارشناسان روابط عمومی | پویانماها و طراحان جلوه‌های ویژه | مسئولان انتخاب بازیگر و استعدادیابی | نویسندگان و پدیدآورندگان</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | درک مطلب | نگارش | شنیدن فعال | تفکر انتقادی | یادگیری فعال | نظارت</t>
+          <t>سخن گفتن | درک مطلب | نگارش | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | ارتباطات و رسانه | حقوق و مقررات دولتی | رایانه و الکترونیک | مخابرات | خدمات مشتریان و خدمات فردی | جغرافیا</t>
+          <t>زبان انگلیسی | ارتباطات و رسانه | قانون و دولت | رایانه و الکترونیک | مخابرات | خدمات مشتری و شخصی | جغرافیا</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | بیان کتبی | وضوح گفتار | درک کتبی | تشخیص گفتار | دید نزدیک | مرتب‌سازی اطلاعات | استدلال استقرایی | حساسیت به مسئله | توجه انتخابی | استدلال قیاسی | روانی ایده‌ها | ابتکار | دید دور | انعطاف‌پذیری درک الگو</t>
+          <t>بیان شفاهی | درک شفاهی | بیان کتبی | وضوح گفتار | درک کتبی | تشخیص گفتار | بینایی نزدیک | ترتیب‌دهی اطلاعات | استدلال استقرایی | حساسیت به مسئله | توجه انتخابی | استدلال قیاسی | روانی ایده‌ها | اصالت | بینایی دور | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>گویندگان پخش و مجریان رادیویی | تحلیل‌گران هوش تجاری | استادان و مدرسان علوم ارتباطات در آموزش عالی | کارمندان مکاتبات اداری | گزارش‌نویسان دادگاه و پیاده‌سازان هم‌زمان گفتار | ویراستاران | تدوین‌گران فیلم و ویدئو | تاریخ‌دانان | تحلیل‌گران اطلاعاتی | مدیران پخش و برنامه‌ریزی رسانه | مدیران فنی رسانه | شاعران، ترانه‌سرایان و نویسندگان خلاق | دانشمندان علوم سیاسی | تهیه‌کنندگان و کارگردانان | نمونه‌خوانان و تصحیح‌کنندگان متون | کارشناسان روابط عمومی | دستیاران پژوهشی علوم اجتماعی | جامعه‌شناسان | نویسندگان متون فنی | نویسندگان و پدیدآورندگان</t>
+          <t>گویندگان پخش و مجریان رادیویی | تحلیل‌گران هوش تجاری | مدرسان علوم ارتباطات در دانشگاه‌ها و مراکز آموزش عالی | کارشناسان مکاتبات و پاسخ‌گویی به شکایات | تندنویسان و ثبت‌کنندگان هم‌زمان صورت‌جلسات | ویراستاران | تدوین‌گران فیلم و ویدیو | مورخان | تحلیل‌گران داده‌ها و اطلاعات امنیتی | مدیران برنامه‌ریزی و پخش رسانه | مدیران فنی رسانه | شاعران، ترانه‌سرایان و نویسندگان خلاق | دانشمندان و پژوهشگران علوم سیاسی | تهیه‌کنندگان و کارگردانان | ویراستاران فنی و نمونه‌خوان‌ها | کارشناسان روابط عمومی | کمک‌کارشناسان و دستیاران پژوهشی علوم اجتماعی | جامعه‌شناسان | نویسندگان متون فنی | نویسندگان و پدیدآورندگان</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ارتباطات و رسانه | زبان انگلیسی | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | فروش و بازاریابی | رایانه و الکترونیک</t>
+          <t>ارتباطات و رسانه | زبان انگلیسی | خدمات مشتری و شخصی | مدیریت و اداره | فروش و بازاریابی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | بیان کتبی | تشخیص گفتار | وضوح گفتار | درک کتبی | حساسیت به مسئله | استدلال قیاسی | روانی ایده‌ها | ابتکار | استدلال استقرایی | دید نزدیک | انعطاف‌پذیری طبقه‌بندی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | بیان شفاهی | بیان کتبی | تشخیص گفتار | وضوح گفتار | درک کتبی | حساسیت به مسئله | استدلال قیاسی | روانی ایده‌ها | اصالت | استدلال استقرایی | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>کارشناسان فروش تبلیغات | مدیران تبلیغات و روابط عمومی | نمایندگان و مدیران برنامه‌های هنرمندان و ورزشکاران | استادان و مدرسان مدیریت بازرگانی در آموزش عالی | مدیران ارشد اجرایی | استادان و مدرسان علوم ارتباطات در آموزش عالی | مسئولان دفاتر و دستیاران اجرایی مدیریت | مسئولان جذب منابع مالی و حامیان مالی | مدیران جذب منابع مالی | تحلیل‌گران فرایندهای سازمانی و مدیریتی | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | مدیران بازاریابی | مدیران پخش و برنامه‌ریزی رسانه | برنامه‌ریزان همایش‌ها، نشست‌ها و رویدادها | مدیران روابط عمومی | مدیران فروش | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، مالی و گردشگری) | استراتژیست‌های بازاریابی موتورهای جستجو | کارشناسان بازاریابی تلفنی | نویسندگان و پدیدآورندگان</t>
+          <t>کارشناسان فروش فضاهای تبلیغاتی | مدیران تبلیغات و روابط ترویجی | مدیران برنامه‌ها و نمایندگان هنرمندان، مجریان و ورزشکاران | استادان علوم اداری و مدیریت، آموزش عالی | مدیران عامل و مدیران ارشد اجرایی | مدرسان علوم ارتباطات در دانشگاه‌ها و مراکز آموزش عالی | مسئولان دفاتر و دستیاران اجرایی مدیریت | کارشناسان جذب منابع مالی و حامی | مدیران جذب منابع مالی و حامیان | کارشناسان تحلیل مدیریت و روش‌ها | کارشناسان تحلیل تحقیقات بازار و بازاریابی | مدیران بازاریابی | مدیران برنامه‌ریزی و پخش رسانه | کارشناسان برنامه‌ریزی و برگزاری همایش‌ها و رویدادها | مدیران روابط عمومی | مدیران فروش | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | کارشناسان تدوین راهبرد بازاریابی موتورهای جستجو | کارشناسان بازاریابی تلفنی | نویسندگان و پدیدآورندگان</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | نگارش | شنیدن فعال | تفکر انتقادی | سخن گفتن | یادگیری فعال | نظارت</t>
+          <t>درک مطلب | نگارش | گوش دادن فعال | تفکر انتقادی | سخن گفتن | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | ارتباطات و رسانه | مدیریت و امور اداری | امور اداری و دفتری | آموزش و پرورش | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک</t>
+          <t>زبان انگلیسی | ارتباطات و رسانه | مدیریت و اداره | اداری | آموزش و پرورش | خدمات مشتری و شخصی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک کتبی | بیان کتبی | درک شفاهی | بیان شفاهی | روانی ایده‌ها | دید نزدیک | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری طبقه‌بندی | ابتکار | استدلال قیاسی | مرتب‌سازی اطلاعات | استدلال استقرایی | حساسیت به مسئله | انعطاف‌پذیری درک الگو | توجه انتخابی</t>
+          <t>درک کتبی | بیان کتبی | درک شفاهی | بیان شفاهی | روانی ایده‌ها | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | اصالت | استدلال قیاسی | ترتیب‌دهی اطلاعات | استدلال استقرایی | حساسیت به مسئله | انعطاف‌پذیری بستار | توجه انتخابی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مدیران هنری | صفحه‌آراها و ناشران رومیزی | متخصصان مدیریت اسناد و مدارک | تدوین‌گران فیلم و ویدئو | طراحان گرافیک | کتابداران و متخصصان آرشیوهای چندرسانه‌ای | استادان و مدرسان علم اطلاعات و دانش‌شناسی در آموزش عالی | تکنسین‌های کتابداری | تحلیل‌گران فرایندهای سازمانی و مدیریتی | مدیران پخش و برنامه‌ریزی رسانه | مدیران فنی رسانه | تحلیل‌گران خبر، خبرنگاران و روزنامه‌نگاران | شاعران، ترانه‌سرایان و نویسندگان خلاق | تهیه‌کنندگان و کارگردانان | نمونه‌خوانان و تصحیح‌کنندگان متون | کارشناسان روابط عمومی | نویسندگان متون فنی | مدیران سیستم‌های وب | طراحان رابط‌های کاربری وب و دیجیتال | نویسندگان و پدیدآورندگان</t>
+          <t>مدیران هنری | متخصصان نشر رومیزی و صفحه‌آرایی دیجیتال | کارشناسان مدیریت اسناد و مدارک | تدوین‌گران فیلم و ویدیو | طراحان گرافیک | کتابداران و کارشناسان مجموعه‌های رسانه‌ای | مدرسان علم اطلاعات و دانش‌شناسی در دانشگاه‌ها و مراکز آموزش عالی | تکنسین‌های کتابداری | کارشناسان تحلیل مدیریت و روش‌ها | مدیران برنامه‌ریزی و پخش رسانه | مدیران فنی رسانه | تحلیل‌گران خبر، خبرنگاران و روزنامه‌نگاران | شاعران، ترانه‌سرایان و نویسندگان خلاق | تهیه‌کنندگان و کارگردانان | ویراستاران فنی و نمونه‌خوان‌ها | کارشناسان روابط عمومی | نویسندگان متون فنی | مدیران وب | طراحان وب و رابط‌های دیجیتال | نویسندگان و پدیدآورندگان</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>نگارش | درک مطلب | شنیدن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | نظارت</t>
+          <t>نگارش | درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | رایانه و الکترونیک | امور اداری و دفتری | ارتباطات و رسانه | مدیریت و امور اداری | ایمنی و امنیت عمومی | آموزش و پرورش | تولید و فراوری</t>
+          <t>زبان انگلیسی | رایانه و الکترونیک | اداری | ارتباطات و رسانه | مدیریت و اداره | ایمنی و امنیت عمومی | آموزش و پرورش | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>بیان کتبی | درک کتبی | دید نزدیک | درک شفاهی | بیان شفاهی | استدلال قیاسی | مرتب‌سازی اطلاعات | حساسیت به مسئله | وضوح گفتار | استدلال استقرایی | تشخیص گفتار | تجسم فضایی | انعطاف‌پذیری طبقه‌بندی | روانی ایده‌ها</t>
+          <t>بیان کتبی | درک کتبی | بینایی نزدیک | درک شفاهی | بیان شفاهی | استدلال قیاسی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | وضوح گفتار | استدلال استقرایی | تشخیص گفتار | تجسم | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مدیران داده‌های بالینی | برنامه‌نویسان رایانه | تحلیل‌گران سیستم‌های رایانه‌ای | مهندسان و معماران سیستم‌های رایانه‌ای | کارمندان مکاتبات اداری | دانشمندان داده | مدیران پایگاه داده | متخصصان مدیریت اسناد و مدارک | ویراستاران | نقشه‌کش‌های برق و الکترونیک | مهندسان صنایع | مدیران پروژه‌های فناوری اطلاعات | تحلیل‌گران فرایندهای سازمانی و مدیریتی | متخصصان مدیریت پروژه | نمونه‌خوانان و تصحیح‌کنندگان متون | دستیاران پژوهشی علوم اجتماعی | توسعه‌دهندگان نرم‌افزار | دستیاران آمار | طراحان رابط‌های کاربری وب و دیجیتال | نویسندگان و پدیدآورندگان</t>
+          <t>مدیران داده‌های بالینی | برنامه‌نویسان کامپیوتر | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | کارشناسان مکاتبات و پاسخ‌گویی به شکایات | دانشمندان داده | مدیران پایگاه داده | کارشناسان مدیریت اسناد و مدارک | ویراستاران | نقشه‌کشان برق و الکترونیک | مهندسان صنایع | مدیران پروژه‌های فناوری اطلاعات | کارشناسان تحلیل مدیریت و روش‌ها | کارشناسان مدیریت پروژه | ویراستاران فنی و نمونه‌خوان‌ها | کمک‌کارشناسان و دستیاران پژوهشی علوم اجتماعی | توسعه‌دهندگان نرم‌افزار | دستیاران و تکنسین‌های آمار | طراحان وب و رابط‌های دیجیتال | نویسندگان و پدیدآورندگان</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>نگارش | درک مطلب | شنیدن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | نظارت</t>
+          <t>نگارش | درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>فروش و بازاریابی | ارتباطات و رسانه | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک</t>
+          <t>فروش و بازاریابی | ارتباطات و رسانه | خدمات مشتری و شخصی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بیان کتبی | درک کتبی | درک شفاهی | بیان شفاهی | روانی ایده‌ها | ابتکار | تشخیص گفتار | وضوح گفتار | دید نزدیک | استدلال استقرایی | استدلال قیاسی | انعطاف‌پذیری طبقه‌بندی | مرتب‌سازی اطلاعات | حساسیت به مسئله</t>
+          <t>بیان کتبی | درک کتبی | درک شفاهی | بیان شفاهی | روانی ایده‌ها | اصالت | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | استدلال استقرایی | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>کارشناسان فروش تبلیغات | مدیران تبلیغات و روابط عمومی | نمایندگان و مدیران برنامه‌های هنرمندان و ورزشکاران | مدیران هنری | ویراستاران | طراحان گرافیک | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | مدیران بازاریابی | مدیران پخش و برنامه‌ریزی رسانه | تحلیل‌گران خبر، خبرنگاران و روزنامه‌نگاران | شاعران، ترانه‌سرایان و نویسندگان خلاق | تهیه‌کنندگان و کارگردانان | نمونه‌خوانان و تصحیح‌کنندگان متون | مدیران روابط عمومی | کارشناسان روابط عمومی | استراتژیست‌های بازاریابی موتورهای جستجو | هنرمندان جلوه‌های ویژه و پویانماها | مدیران جذب استعدادهای هنری | نویسندگان متون فنی | طراحان رابط‌های کاربری وب و دیجیتال</t>
+          <t>کارشناسان فروش فضاهای تبلیغاتی | مدیران تبلیغات و روابط ترویجی | مدیران برنامه‌ها و نمایندگان هنرمندان، مجریان و ورزشکاران | مدیران هنری | ویراستاران | طراحان گرافیک | کارشناسان تحلیل تحقیقات بازار و بازاریابی | مدیران بازاریابی | مدیران برنامه‌ریزی و پخش رسانه | تحلیل‌گران خبر، خبرنگاران و روزنامه‌نگاران | شاعران، ترانه‌سرایان و نویسندگان خلاق | تهیه‌کنندگان و کارگردانان | ویراستاران فنی و نمونه‌خوان‌ها | مدیران روابط عمومی | کارشناسان روابط عمومی | کارشناسان تدوین راهبرد بازاریابی موتورهای جستجو | پویانماها و طراحان جلوه‌های ویژه | مسئولان انتخاب بازیگر و استعدادیابی | نویسندگان متون فنی | طراحان وب و رابط‌های دیجیتال</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>نگارش | درک مطلب | سخن گفتن | تفکر انتقادی | یادگیری فعال | شنیدن فعال</t>
+          <t>نگارش | درک مطلب | سخن گفتن | تفکر انتقادی | یادگیری فعال | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | ارتباطات و رسانه | رایانه و الکترونیک | امور اداری و دفتری | فروش و بازاریابی | هنرهای زیبا</t>
+          <t>زبان انگلیسی | ارتباطات و رسانه | رایانه و الکترونیک | اداری | فروش و بازاریابی | هنرهای زیبا</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>بیان کتبی | روانی ایده‌ها | درک کتبی | ابتکار | درک شفاهی | دید نزدیک | بیان شفاهی | استدلال استقرایی | انعطاف‌پذیری طبقه‌بندی | مرتب‌سازی اطلاعات | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | توجه انتخابی</t>
+          <t>بیان کتبی | روانی ایده‌ها | درک کتبی | اصالت | درک شفاهی | بینایی نزدیک | بیان شفاهی | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | توجه انتخابی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>بازیگران | مدیران هنری | استادان و مدرسان هنر، تئاتر و موسیقی در آموزش عالی | گویندگان پخش و مجریان رادیویی | موزه‌داران | ویراستاران | استادان و مدرسان زبان و ادبیات انگلیسی در آموزش عالی | تدوین‌گران فیلم و ویدئو | هنرمندان هنرهای تجسمی شامل نقاشان، مجسمه‌سازان و تصویرگران | طراحان گرافیک | تاریخ‌دانان | مدیران موسیقی و آهنگسازان | تحلیل‌گران خبر، خبرنگاران و روزنامه‌نگاران | تهیه‌کنندگان و کارگردانان | نمونه‌خوانان و تصحیح‌کنندگان متون | کارشناسان روابط عمومی | هنرمندان جلوه‌های ویژه و پویانماها | مدیران جذب استعدادهای هنری | نویسندگان متون فنی | نویسندگان و پدیدآورندگان</t>
+          <t>بازیگران | مدیران هنری | مدرسان هنرهای تجسمی، نمایشی و موسیقی در دانشگاه‌ها و مراکز آموزش عالی | گویندگان پخش و مجریان رادیویی | موزه‌داران | ویراستاران | مدرسان زبان و ادبیات انگلیسی در دانشگاه‌ها و مراکز آموزش عالی | تدوین‌گران فیلم و ویدیو | هنرمندان هنرهای تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | طراحان گرافیک | مورخان | رهبران ارکستر، مدیران موسیقی و آهنگسازان | تحلیل‌گران خبر، خبرنگاران و روزنامه‌نگاران | تهیه‌کنندگان و کارگردانان | ویراستاران فنی و نمونه‌خوان‌ها | کارشناسان روابط عمومی | پویانماها و طراحان جلوه‌های ویژه | مسئولان انتخاب بازیگر و استعدادیابی | نویسندگان متون فنی | نویسندگان و پدیدآورندگان</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
